--- a/tests/TC-11/results/teacher_timetables_even.xlsx
+++ b/tests/TC-11/results/teacher_timetables_even.xlsx
@@ -11,7 +11,12 @@
     <sheet name="Dr. Anand" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Dr. Eswaran" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Dr. Guha" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dr. Sandesh" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dr. Layek" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dr. Physics" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Dr. Prabhu" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Dr. Rajendra" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dr. Sandesh" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Dr. Vivekraj" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +43,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +74,12 @@
         <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -88,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,6 +117,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -631,27 +645,27 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>CS154
 Room: 103</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>CS154
 Room: 103</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>CS154
 Room: 103</t>
         </is>
       </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -673,14 +687,405 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>CS154
 Room: 103</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj  Weekly Timetable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11:00-11:30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>11:30-12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:30-13:15</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>18:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -752,30 +1157,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -964,8 +1349,20 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -990,27 +1387,9 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1032,18 +1411,30 @@
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>MA163 TUT
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -1064,20 +1455,8 @@
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -1106,9 +1485,27 @@
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
@@ -1285,27 +1682,27 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>EC156
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>EC156
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
+Room: 101</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>EC156
-Room: 102</t>
-        </is>
-      </c>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -1327,12 +1724,7 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -1352,9 +1744,24 @@
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -1405,31 +1812,31 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>EC156
-Room: 102</t>
+Room: 101</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>EC156
-Room: 102</t>
+Room: 101</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>EC156
-Room: 102</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 102</t>
-        </is>
-      </c>
+Room: 101</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -1661,26 +2068,26 @@
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -1700,38 +2107,26 @@
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>CS162 LEC
 (CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+Room: 102</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>CS162 LEC
 (CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+Room: 102</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -1747,20 +2142,8 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1776,7 +2159,13 @@
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>CS162 TUT
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1794,7 +2183,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -1822,7 +2211,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dr. Sandesh  Weekly Timetable</t>
+          <t>Dr. Layek  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -1954,24 +2343,9 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -1993,18 +2367,337 @@
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dr. Physics  Weekly Timetable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11:00-11:30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>11:30-12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:30-13:15</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>18:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 101</t>
+        </is>
+      </c>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
@@ -2055,6 +2748,332 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 101</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 101</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dr. Prabhu  Weekly Timetable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11:00-11:30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>11:30-12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:30-13:15</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>18:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
@@ -2072,30 +3091,10 @@
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -2114,4 +3113,662 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dr. Rajendra  Weekly Timetable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11:00-11:30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>11:30-12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:30-13:15</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>18:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh  Weekly Timetable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11:00-11:30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>11:30-12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:30-13:15</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>18:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 101</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tests/TC-11/results/teacher_timetables_even.xlsx
+++ b/tests/TC-11/results/teacher_timetables_even.xlsx
@@ -634,8 +634,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -645,24 +655,9 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
@@ -681,9 +676,24 @@
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
@@ -707,24 +717,9 @@
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -732,9 +727,24 @@
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>CS154
+Room: 103</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -775,30 +785,10 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CS154
-Room: 103</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -975,34 +965,10 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
@@ -1024,68 +990,32 @@
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>CS163 LAB
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
 (CSE_2_B)
-Room: L101+L102</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>CS163 LAB
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
 (CSE_2_B)
-Room: L101+L102</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>CS163 LAB
-(CSE_2_B)
-Room: L101+L102</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>CS163 LAB
-(CSE_2_B)
-Room: L101+L102</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>CS163 LAB
-(CSE_2_B)
-Room: L101+L102</t>
-        </is>
-      </c>
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
@@ -1137,9 +1067,27 @@
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>CS163 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
@@ -1165,11 +1113,41 @@
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>CS163 LAB
+(CSE_2_B)
+Room: L101+L102</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
@@ -1337,10 +1315,34 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
@@ -1349,20 +1351,8 @@
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>MA163 TUT
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S3" s="6" t="inlineStr">
-        <is>
-          <t>MA163 TUT
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -1388,8 +1378,20 @@
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -1410,31 +1412,25 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>MA163 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>MA163 LEC
 (CSE_2_B)
 Room: 101</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -1485,27 +1481,9 @@
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
@@ -1671,8 +1649,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1682,24 +1670,9 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 101</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 101</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 101</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1718,9 +1691,24 @@
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 101</t>
+        </is>
+      </c>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
@@ -1744,24 +1732,9 @@
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 102</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -1769,9 +1742,24 @@
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>EC156
+Room: 102</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -1812,30 +1800,10 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>EC156
-Room: 101</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
@@ -2020,8 +1988,20 @@
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -2074,20 +2054,8 @@
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -2113,41 +2081,65 @@
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>CS162 TUT
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>CS162 TUT
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>CS162 LEC
 (CSE_2_B)
 Room: 102</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>CS162 LEC
 (CSE_2_B)
 Room: 102</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="35" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>CS162 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
@@ -2159,13 +2151,7 @@
       <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2346,7 +2332,12 @@
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -2366,8 +2357,18 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -2385,15 +2386,30 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>DS151
 Room: 102</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>DS151
+Room: 102</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
@@ -2416,30 +2432,10 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -2462,12 +2458,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>DS151
-Room: 102</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -2661,9 +2652,24 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
@@ -2692,12 +2698,7 @@
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>HS159
-Room: 101</t>
-        </is>
-      </c>
+      <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
@@ -2714,8 +2715,18 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
@@ -2735,10 +2746,30 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>HS159
+Room: 102</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -2748,24 +2779,9 @@
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>HS159
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>HS159
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S6" s="4" t="inlineStr">
-        <is>
-          <t>HS159
-Room: 101</t>
-        </is>
-      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
     </row>
@@ -2786,18 +2802,8 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>HS159
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>HS159
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -3021,20 +3027,8 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -3097,8 +3091,20 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>CS208 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -3285,7 +3291,12 @@
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -3305,8 +3316,18 @@
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -3324,15 +3345,30 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>CS151
 Room: 101</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>CS151
+Room: 101</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
@@ -3355,30 +3391,10 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
@@ -3401,12 +3417,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>CS151
-Room: 101</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
@@ -3587,8 +3598,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 101</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
@@ -3598,24 +3619,9 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
@@ -3634,9 +3640,24 @@
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 102</t>
+        </is>
+      </c>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
@@ -3660,24 +3681,9 @@
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 101</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -3685,9 +3691,24 @@
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>ASD152
+Room: 101</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
@@ -3728,30 +3749,10 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>ASD152
-Room: 102</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
